--- a/AAII_Financials/Quarterly/MAGN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MAGN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="92">
   <si>
     <t>MAGN</t>
   </si>
@@ -656,71 +656,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E7" s="2">
         <v>46109</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46018</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45836</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45745</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45654</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45563</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45472</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45381</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45290</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -739,44 +740,47 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>857000</v>
+      </c>
+      <c r="E8" s="3">
         <v>796000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>792000</v>
-      </c>
-      <c r="F8" s="3">
-        <v>839000</v>
       </c>
       <c r="G8" s="3">
         <v>839000</v>
       </c>
       <c r="H8" s="3">
+        <v>839000</v>
+      </c>
+      <c r="I8" s="3">
         <v>824000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>702000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>554000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>556000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>558000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>519000</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -795,44 +799,47 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>745000</v>
+      </c>
+      <c r="E9" s="3">
         <v>701000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>695000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>751000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>749000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>736000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>631000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>496000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>489000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>488000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>477000</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -851,44 +858,47 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E10" s="3">
         <v>95000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>97000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>88000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>90000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>88000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>71000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>58000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>67000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>70000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>42000</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -907,8 +917,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -929,8 +942,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -940,24 +954,24 @@
       <c r="E12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3">
         <v>20000</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3">
         <v>13000</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -985,8 +999,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1041,35 +1058,38 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E14" s="3">
         <v>16000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>22000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>75000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3">
+        <v>14000</v>
+      </c>
+      <c r="I14" s="3">
         <v>23000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>47000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>202000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1097,31 +1117,34 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E15" s="3">
         <v>12000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>11000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>13000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>14000</v>
       </c>
       <c r="I15" s="3">
         <v>14000</v>
       </c>
       <c r="J15" s="3">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="K15" s="3">
         <v>12000</v>
@@ -1133,13 +1156,13 @@
         <v>12000</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
@@ -1153,8 +1176,11 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1172,44 +1198,45 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>812000</v>
+      </c>
+      <c r="E17" s="3">
         <v>763000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>756000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>754000</v>
       </c>
-      <c r="G17" s="3">
-        <v>826000</v>
-      </c>
       <c r="H17" s="3">
+        <v>812000</v>
+      </c>
+      <c r="I17" s="3">
         <v>797000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>692000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>519000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>539000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>533000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>521000</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1228,44 +1255,47 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E18" s="3">
         <v>33000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>36000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>85000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>13000</v>
       </c>
       <c r="H18" s="3">
         <v>27000</v>
       </c>
       <c r="I18" s="3">
+        <v>27000</v>
+      </c>
+      <c r="J18" s="3">
         <v>10000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>35000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>25000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2000</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1284,8 +1314,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1306,44 +1339,45 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4000</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="H20" s="3">
         <v>2000</v>
       </c>
       <c r="I20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J20" s="3">
         <v>4000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-8000</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>5000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8000</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1362,49 +1396,52 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E21" s="3">
         <v>48000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>46000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>90000</v>
       </c>
-      <c r="G21" s="3">
-        <v>26000</v>
-      </c>
       <c r="H21" s="3">
+        <v>38000</v>
+      </c>
+      <c r="I21" s="3">
         <v>39000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>20000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>55000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>29000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>32000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2000</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
       <c r="O21" s="3">
         <v>0</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
+      <c r="P21" s="3">
+        <v>0</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
@@ -1418,41 +1455,44 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E22" s="3">
         <v>37000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>42000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>39000</v>
       </c>
-      <c r="G22" s="3">
-        <v>37000</v>
-      </c>
       <c r="H22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="I22" s="3">
         <v>42000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>28000</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>1000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2000</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1474,44 +1514,47 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-29000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-33000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-24000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-40000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-69000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-159000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>16000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>18000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10000</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1530,44 +1573,47 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-6000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-9000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>20000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2000</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1586,8 +1632,11 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1642,44 +1691,47 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-18000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-34000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-40000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-18000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-41000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-60000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-179000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8000</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,44 +1750,47 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-18000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-34000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-40000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-18000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-41000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-60000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-179000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>14000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8000</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1754,8 +1809,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1810,8 +1868,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1851,8 +1912,8 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>3</v>
@@ -1866,8 +1927,11 @@
       <c r="T29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1922,8 +1986,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1978,44 +2045,47 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E32" s="3">
         <v>3000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4000</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="H32" s="3">
         <v>-2000</v>
       </c>
       <c r="I32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J32" s="3">
         <v>-4000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>8000</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>-5000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8000</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2034,44 +2104,47 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-18000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-34000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-40000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-18000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-41000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-60000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-179000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>14000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8000</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2090,8 +2163,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2146,44 +2222,47 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-18000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-34000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-40000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-18000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-41000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-60000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-179000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>14000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8000</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2202,49 +2281,52 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E38" s="2">
         <v>46109</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46018</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45836</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45745</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45654</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45563</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45472</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45381</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45290</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2263,8 +2345,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2285,8 +2370,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2307,38 +2393,39 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>280000</v>
+      </c>
+      <c r="E41" s="3">
         <v>303000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>264000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>305000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>276000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>282000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>215000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>230000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>176000</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2363,8 +2450,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2404,8 +2494,8 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
@@ -2419,38 +2509,41 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>531000</v>
+      </c>
+      <c r="E43" s="3">
         <v>536000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>553000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>522000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>517000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>492000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>475000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>359000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>347000</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2475,38 +2568,41 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>498000</v>
+      </c>
+      <c r="E44" s="3">
         <v>472000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>476000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>474000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>535000</v>
-      </c>
-      <c r="H44" s="3">
-        <v>508000</v>
       </c>
       <c r="I44" s="3">
         <v>508000</v>
       </c>
       <c r="J44" s="3">
+        <v>508000</v>
+      </c>
+      <c r="K44" s="3">
         <v>259000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>287000</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2531,8 +2627,11 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2587,38 +2686,41 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1392000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1407000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1365000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1423000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1484000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1428000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1338000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>886000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>872000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2643,8 +2745,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2699,38 +2804,41 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1451000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1483000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1513000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>1538000</v>
       </c>
       <c r="G48" s="3">
         <v>1538000</v>
       </c>
       <c r="H48" s="3">
+        <v>1538000</v>
+      </c>
+      <c r="I48" s="3">
         <v>1590000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1606000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>998000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1006000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2755,43 +2863,46 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>858000</v>
+      </c>
+      <c r="E49" s="3">
         <v>870000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>880000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>890000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>937000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>890000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>876000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>850000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1027000</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
+      <c r="N49" s="3">
+        <v>0</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
@@ -2811,8 +2922,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2867,8 +2981,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2923,38 +3040,41 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E52" s="3">
         <v>136000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>135000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>62000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>153000</v>
       </c>
       <c r="H52" s="3">
         <v>153000</v>
       </c>
       <c r="I52" s="3">
+        <v>153000</v>
+      </c>
+      <c r="J52" s="3">
         <v>173000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>71000</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2979,8 +3099,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3035,38 +3158,41 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3834000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3896000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3893000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3989000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4112000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4061000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3993000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2807000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2976000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3091,8 +3217,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3113,8 +3242,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3135,38 +3265,39 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>361000</v>
+      </c>
+      <c r="E57" s="3">
         <v>369000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>326000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>356000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>393000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>379000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>333000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>295000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>238000</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3191,43 +3322,46 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E58" s="3">
         <v>17000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>18000</v>
       </c>
       <c r="F58" s="3">
         <v>18000</v>
       </c>
       <c r="G58" s="3">
+        <v>18000</v>
+      </c>
+      <c r="H58" s="3">
         <v>27000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>26000</v>
       </c>
       <c r="I58" s="3">
         <v>26000</v>
       </c>
       <c r="J58" s="3">
-        <v>11000</v>
+        <v>26000</v>
       </c>
       <c r="K58" s="3">
         <v>11000</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
+      <c r="N58" s="3">
+        <v>0</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
@@ -3247,35 +3381,38 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>104000</v>
+      </c>
+      <c r="E59" s="3">
         <v>138000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>132000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>137000</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>104000</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3303,38 +3440,41 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>569000</v>
+      </c>
+      <c r="E60" s="3">
         <v>605000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>556000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>601000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>584000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>596000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>546000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>457000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>375000</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3359,38 +3499,41 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1943000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1942000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1975000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1997000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2039000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>2045000</v>
       </c>
       <c r="I61" s="3">
         <v>2045000</v>
       </c>
       <c r="J61" s="3">
+        <v>2045000</v>
+      </c>
+      <c r="K61" s="3">
         <v>39000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>38000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3400,8 +3543,8 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3" t="s">
-        <v>3</v>
+      <c r="P61" s="3">
+        <v>0</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>3</v>
@@ -3415,38 +3558,41 @@
       <c r="T61" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>255000</v>
+      </c>
+      <c r="E62" s="3">
         <v>258000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>276000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>281000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>285000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>226000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>186000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>94000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>97000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3617,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3527,8 +3676,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3583,8 +3735,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3639,38 +3794,41 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2817000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2857000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2855000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2925000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2981000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2968000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2887000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>668000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>582000</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3695,8 +3853,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3717,8 +3878,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3773,8 +3935,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3829,8 +3994,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3870,8 +4038,8 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3" t="s">
-        <v>3</v>
+      <c r="P70" s="3">
+        <v>0</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>3</v>
@@ -3885,8 +4053,11 @@
       <c r="T70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3941,32 +4112,35 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-231000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-211000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-193000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-159000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-119000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-101000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-60000</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3997,8 +4171,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4053,8 +4230,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4109,8 +4289,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4165,44 +4348,47 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1017000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1039000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1038000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1064000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1131000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1093000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1106000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2139000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2394000</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3">
         <v>2390000</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4221,8 +4407,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4277,49 +4466,52 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E80" s="2">
         <v>46109</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46018</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45836</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45745</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45654</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45563</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45472</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45381</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45290</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4338,44 +4530,47 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-18000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-34000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-40000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-18000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-41000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-60000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-179000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>14000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8000</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4394,8 +4589,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4416,35 +4614,36 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E83" s="3">
         <v>44000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>39000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>33000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>31000</v>
       </c>
       <c r="H83" s="3">
         <v>31000</v>
       </c>
       <c r="I83" s="3">
+        <v>31000</v>
+      </c>
+      <c r="J83" s="3">
         <v>32000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>30000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4472,8 +4671,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4528,8 +4730,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4584,8 +4789,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4640,8 +4848,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4696,8 +4907,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4752,44 +4966,47 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E89" s="3">
         <v>87000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>96000</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>65000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-58000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>161000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>38000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>20000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-27000</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4808,8 +5025,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4830,44 +5050,45 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14000</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-15000</v>
       </c>
       <c r="F91" s="3">
         <v>-15000</v>
       </c>
       <c r="G91" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="H91" s="3">
         <v>-13000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-23000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-16000</v>
       </c>
       <c r="J91" s="3">
         <v>-16000</v>
       </c>
       <c r="K91" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="L91" s="3">
         <v>-15000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-25000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16000</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4886,8 +5107,11 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4942,8 +5166,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4998,44 +5225,47 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14000</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-15000</v>
       </c>
       <c r="F94" s="3">
         <v>-15000</v>
       </c>
       <c r="G94" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="H94" s="3">
         <v>-13000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>21000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-27000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>14000</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5054,8 +5284,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5076,8 +5309,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5087,8 +5321,8 @@
       <c r="E96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -5097,11 +5331,11 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>1111000</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
@@ -5132,8 +5366,11 @@
       <c r="T96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5188,8 +5425,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5244,8 +5484,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5300,44 +5543,47 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-36000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-27000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-49000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>33000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-98000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-18000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>16000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5356,35 +5602,38 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E101" s="3">
         <v>4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-11000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4000</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5412,49 +5661,52 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E102" s="3">
         <v>39000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-41000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>29000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>67000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>54000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18000</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
+      <c r="P102" s="3">
+        <v>0</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
@@ -5466,6 +5718,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
